--- a/StructureDefinition-event-list.xlsx
+++ b/StructureDefinition-event-list.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/event-list</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/event-list</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T13:18:28+00:00</t>
+    <t>2026-10-29T07:06:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -577,7 +577,7 @@
     <t>Lists often contain subsets of resources rather than an exhaustive list.  The code identifies what type of subset is included.</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/ValueSet/list-purposes</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/ValueSet/list-purposes</t>
   </si>
   <si>
     <t>.code</t>
@@ -1319,7 +1319,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.66015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.2109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.1953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-event-list.xlsx
+++ b/StructureDefinition-event-list.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:06:30+00:00</t>
+    <t>2026-10-29T08:26:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-event-list.xlsx
+++ b/StructureDefinition-event-list.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:26:45+00:00</t>
+    <t>2026-10-29T09:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-event-list.xlsx
+++ b/StructureDefinition-event-list.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:23:29+00:00</t>
+    <t>2026-10-29T13:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-event-list.xlsx
+++ b/StructureDefinition-event-list.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:05:39+00:00</t>
+    <t>2026-10-29T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-event-list.xlsx
+++ b/StructureDefinition-event-list.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T15:50:41+00:00</t>
+    <t>2026-10-29T16:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-event-list.xlsx
+++ b/StructureDefinition-event-list.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T16:44:10+00:00</t>
+    <t>2026-10-30T09:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
